--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd9adf649fe44224"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rccf20c8ffc05443b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc420507880e643e3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64c2868e32854210"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73308ad9ab734344"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d9763c3e7de4abf"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rccf20c8ffc05443b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9348ac2dcf4e4af0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64c2868e32854210"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R627c18d52e264ef2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d9763c3e7de4abf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6368e2c59c4058"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9348ac2dcf4e4af0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7be28cb598c24544"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R627c18d52e264ef2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29e699adc58c4910"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f6368e2c59c4058"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cbdfaa64a7c4b64"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7be28cb598c24544"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e5b840e10414d2b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R29e699adc58c4910"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44aa8220f7b94595"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cbdfaa64a7c4b64"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08a27731568a4650"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e5b840e10414d2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec0d9538dff14625"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R44aa8220f7b94595"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb25d78bc71284a1d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08a27731568a4650"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reea89710a59f4c0a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rec0d9538dff14625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d2302e2a8bd4ccd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb25d78bc71284a1d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bd685d4c5594b39"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reea89710a59f4c0a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22a6170504fd4ed9"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d2302e2a8bd4ccd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04de813554df4327"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3bd685d4c5594b39"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R253658ce6b044bf3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22a6170504fd4ed9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R439e71e0eb344275"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R04de813554df4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1782c87b4c204fbf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R253658ce6b044bf3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1be890ccfb7a464f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R439e71e0eb344275"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46f7787862bb4cad"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1782c87b4c204fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re34b015402f14008"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1be890ccfb7a464f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06664ecb6685425a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46f7787862bb4cad"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2278dcc6bf5d450f"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re34b015402f14008"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95a0feb9d4344025"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06664ecb6685425a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64e2447d42884913"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2278dcc6bf5d450f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f59c00a42824522"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95a0feb9d4344025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e1635aea52d4f1f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R64e2447d42884913"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd335bd0f94f74666"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f59c00a42824522"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97a0617162d64ffe"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1e1635aea52d4f1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c51d61fafee4128"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd335bd0f94f74666"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd7c62b3f5d9f403c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97a0617162d64ffe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c278fedf7904ea6"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3c51d61fafee4128"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b9de42adc6b4539"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd7c62b3f5d9f403c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raaae1c32b8ab42d9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c278fedf7904ea6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R952d2055984746d1"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8b9de42adc6b4539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e7f4379fb254541"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raaae1c32b8ab42d9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6f97a06e9094fee"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R952d2055984746d1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41f07f79ba04424a"/>
 </x:worksheet>
 </file>
--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ChartBar/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e7f4379fb254541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1906051194e24d76"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -140,7 +140,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6f97a06e9094fee"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R58ba8c523d9b4866"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -177,6 +177,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41f07f79ba04424a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4acc48dc770c4715"/>
 </x:worksheet>
 </file>